--- a/JsonConverter/ExcelFiles/FighterData.xlsx
+++ b/JsonConverter/ExcelFiles/FighterData.xlsx
@@ -12,166 +12,172 @@
     <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="13035"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
+    <x:sheet name="FighterData" sheetId="1" r:id="rId4"/>
   </x:sheets>
   <x:calcPr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" mc:Ignorable="hs" hs:hclCalcId="904"/>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="51">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="53">
+  <x:si>
+    <x:t>리치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_elbow,skill_uppercut,skill_takedown_judo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_elbow,skill_uppercut,skill_takedown_judo,skill_guillotine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김기본</x:t>
+  </x:si>
   <x:si>
     <x:t>김종합</x:t>
   </x:si>
   <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
     <x:t>김타격</x:t>
   </x:si>
   <x:si>
-    <x:t>김기본</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
     <x:t>Hp</x:t>
   </x:si>
   <x:si>
+    <x:t>StartingSkillIds</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_guillotine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WrestlingDefense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_takedown_judo</x:t>
+  </x:si>
+  <x:si>
     <x:t>WrestlingOffense</x:t>
   </x:si>
   <x:si>
-    <x:t>skill_guillotine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_takedown_judo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StartingSkillIds</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WrestlingDefense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_elbow,skill_uppercut,skill_takedown_judo</x:t>
+    <x:t>김레슬러</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Stamina</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주짓수위주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김클린치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김그래플러</x:t>
+  </x:si>
+  <x:si>
+    <x:t>션 스트릭랜드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김주짓수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레슬링위주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클린치위주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타격위주</x:t>
   </x:si>
   <x:si>
     <x:t>Description</x:t>
   </x:si>
   <x:si>
+    <x:t>fighter_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_04</x:t>
+  </x:si>
+  <x:si>
     <x:t>fighter_02</x:t>
   </x:si>
   <x:si>
+    <x:t>fighter_07</x:t>
+  </x:si>
+  <x:si>
     <x:t>fighter_05</x:t>
   </x:si>
   <x:si>
     <x:t>캐릭터 고유 ID</x:t>
   </x:si>
   <x:si>
-    <x:t>fighter_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_07</x:t>
-  </x:si>
-  <x:si>
     <x:t>fighter_08</x:t>
   </x:si>
   <x:si>
+    <x:t>BodyAddress</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 캐릭터이다</x:t>
+  </x:si>
+  <x:si>
     <x:t>fighter_01</x:t>
   </x:si>
   <x:si>
-    <x:t>BodyAddress</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 캐릭터이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Stamina</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주짓수위주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김클린치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김레슬러</x:t>
-  </x:si>
-  <x:si>
-    <x:t>션 스트릭랜드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김그래플러</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김주짓수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레슬링위주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타격위주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>클린치위주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_elbow,skill_uppercut,skill_takedown_judo,skill_guillotine</x:t>
+    <x:t>타격, 테이크다운 방어 위주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레슬링과 Ground 테스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JiuJitsuOffense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TrainingStamina</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StandingDefense</x:t>
   </x:si>
   <x:si>
     <x:t>StandingOffense</x:t>
   </x:si>
   <x:si>
-    <x:t>TrainingStamina</x:t>
+    <x:t>JiuJitsuDefense</x:t>
   </x:si>
   <x:si>
     <x:t>구현된 특수기술 전체 테스트</x:t>
   </x:si>
   <x:si>
-    <x:t>StandingDefense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레슬링과 Ground 테스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타격, 테이크다운 방어 위주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JiuJitsuOffense</x:t>
-  </x:si>
-  <x:si>
     <x:t>PortraitAddress</x:t>
   </x:si>
   <x:si>
-    <x:t>JiuJitsuDefense</x:t>
+    <x:t>KimBasic[south-east 1_1]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_elbow,skill_uppercut</x:t>
   </x:si>
   <x:si>
     <x:t>KimBasic[south-east 1_0]</x:t>
   </x:si>
   <x:si>
-    <x:t>KimBasic[south-east 1_1]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_elbow,skill_uppercut</x:t>
+    <x:t>Reach</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -942,7 +948,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:O35"/>
+  <x:dimension ref="A1:P35"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="25.4296875" style="1" customWidth="1"/>
@@ -954,126 +960,135 @@
     <x:col min="9" max="9" width="20" style="1" customWidth="1"/>
     <x:col min="10" max="10" width="18.85546875" style="1" customWidth="1"/>
     <x:col min="11" max="12" width="18" style="1" customWidth="1"/>
-    <x:col min="13" max="13" width="18.85546875" style="1" customWidth="1"/>
-    <x:col min="14" max="14" width="18.4296875" style="1" customWidth="1"/>
-    <x:col min="15" max="15" width="17.14453125" style="1" customWidth="1"/>
-    <x:col min="16" max="16384" width="12.54296875" style="1"/>
+    <x:col min="13" max="14" width="18.85546875" style="1" customWidth="1"/>
+    <x:col min="15" max="15" width="18.4296875" style="1" customWidth="1"/>
+    <x:col min="16" max="16" width="17.14453125" style="1" customWidth="1"/>
+    <x:col min="17" max="16384" width="12.54296875" style="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:1" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="N1" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:16" ht="13.199999999999999">
+      <x:c r="A2" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:15" ht="13.199999999999999">
-      <x:c r="A2" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="J2" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="K2" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="L2" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="M2" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="N2" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="O2" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:15" s="7" customFormat="1" ht="15.75" customHeight="1">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="P2" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:16" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D3" s="2" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E3" s="2" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F3" s="7" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G3" s="7" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H3" s="7" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="I3" s="7" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="J3" s="7" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="K3" s="7" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L3" s="7" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="M3" s="7" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N3" s="7" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="O3" s="7" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="P3" s="7" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="A4" s="3" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B4" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B3" s="2" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C3" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D3" s="2" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E3" s="2" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F3" s="7" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G3" s="7" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="H3" s="7" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="I3" s="7" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="J3" s="7" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="K3" s="7" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="L3" s="7" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="M3" s="7" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="N3" s="7" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="O3" s="7" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A4" s="3" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B4" s="3" t="s">
-        <x:v>2</x:v>
-      </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>22</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D4" s="5" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="E4" s="5" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F4" s="1">
         <x:v>150</x:v>
@@ -1100,27 +1115,30 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="N4" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O4" s="1">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="O4" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P4" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>28</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>32</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D5" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E5" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F5" s="1">
         <x:v>150</x:v>
@@ -1147,27 +1165,30 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="N5" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O5" s="1">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O5" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P5" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>31</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>26</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D6" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E6" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F6" s="1">
         <x:v>170</x:v>
@@ -1194,27 +1215,30 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="N6" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O6" s="1">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O6" s="1" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P6" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>17</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D7" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E7" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F7" s="1">
         <x:v>250</x:v>
@@ -1241,27 +1265,30 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O7" s="1">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O7" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P7" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C8" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D8" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E8" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F8" s="1">
         <x:v>270</x:v>
@@ -1288,27 +1315,30 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="N8" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O8" s="1">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O8" s="1" t="s">
+      <x:c r="P8" s="1" t="s">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
+    <x:row r="9" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A9" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C9" s="5" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D9" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E9" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F9" s="1">
         <x:v>300</x:v>
@@ -1335,27 +1365,30 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="N9" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O9" s="1">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O9" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P9" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C10" s="5" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D10" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E10" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F10" s="1">
         <x:v>350</x:v>
@@ -1382,27 +1415,30 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="N10" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O10" s="1">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O10" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P10" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A11" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F11" s="1">
         <x:v>400</x:v>
@@ -1429,10 +1465,13 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="N11" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O11" s="1">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O11" s="1" t="s">
-        <x:v>38</x:v>
+      <x:c r="P11" s="1" t="s">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/FighterData.xlsx
+++ b/JsonConverter/ExcelFiles/FighterData.xlsx
@@ -19,165 +19,174 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="53">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="56">
+  <x:si>
+    <x:t>선호사거리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_takedown_judo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StartingSkillIds</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WrestlingDefense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_guillotine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WrestlingOffense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PreferredMinDistance</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PreferredMaxDistance</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
   <x:si>
     <x:t>리치</x:t>
   </x:si>
   <x:si>
+    <x:t>Hp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김종합</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김기본</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김타격</x:t>
+  </x:si>
+  <x:si>
     <x:t>skill_elbow,skill_uppercut,skill_takedown_judo</x:t>
   </x:si>
   <x:si>
     <x:t>skill_elbow,skill_uppercut,skill_takedown_judo,skill_guillotine</x:t>
   </x:si>
   <x:si>
-    <x:t>김기본</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김종합</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김타격</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StartingSkillIds</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_guillotine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WrestlingDefense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_takedown_judo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WrestlingOffense</x:t>
+    <x:t>BodyAddress</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 캐릭터이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>션 스트릭랜드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클린치위주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김그래플러</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김클린치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Reach</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김주짓수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레슬링위주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타격위주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주짓수위주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
   </x:si>
   <x:si>
     <x:t>김레슬러</x:t>
   </x:si>
   <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
     <x:t>Stamina</x:t>
   </x:si>
   <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주짓수위주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김클린치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김그래플러</x:t>
-  </x:si>
-  <x:si>
-    <x:t>션 스트릭랜드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김주짓수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레슬링위주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>클린치위주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타격위주</x:t>
+    <x:t>fighter_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_05</x:t>
   </x:si>
   <x:si>
     <x:t>Description</x:t>
   </x:si>
   <x:si>
-    <x:t>fighter_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_06</x:t>
-  </x:si>
-  <x:si>
     <x:t>fighter_04</x:t>
   </x:si>
   <x:si>
     <x:t>fighter_02</x:t>
   </x:si>
   <x:si>
-    <x:t>fighter_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_05</x:t>
-  </x:si>
-  <x:si>
     <x:t>캐릭터 고유 ID</x:t>
   </x:si>
   <x:si>
-    <x:t>fighter_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BodyAddress</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 캐릭터이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_01</x:t>
+    <x:t>KimBasic[south-east 1_0]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KimBasic[south-east 1_1]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_elbow,skill_uppercut</x:t>
   </x:si>
   <x:si>
     <x:t>타격, 테이크다운 방어 위주</x:t>
   </x:si>
   <x:si>
+    <x:t>TrainingStamina</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JiuJitsuOffense</x:t>
+  </x:si>
+  <x:si>
     <x:t>레슬링과 Ground 테스트</x:t>
   </x:si>
   <x:si>
-    <x:t>JiuJitsuOffense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TrainingStamina</x:t>
+    <x:t>StandingOffense</x:t>
   </x:si>
   <x:si>
     <x:t>StandingDefense</x:t>
   </x:si>
   <x:si>
-    <x:t>StandingOffense</x:t>
+    <x:t>PortraitAddress</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구현된 특수기술 전체 테스트</x:t>
   </x:si>
   <x:si>
     <x:t>JiuJitsuDefense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구현된 특수기술 전체 테스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PortraitAddress</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KimBasic[south-east 1_1]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_elbow,skill_uppercut</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KimBasic[south-east 1_0]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Reach</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -948,7 +957,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:P35"/>
+  <x:dimension ref="A1:R35"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="25.4296875" style="1" customWidth="1"/>
@@ -961,34 +970,41 @@
     <x:col min="10" max="10" width="18.85546875" style="1" customWidth="1"/>
     <x:col min="11" max="12" width="18" style="1" customWidth="1"/>
     <x:col min="13" max="14" width="18.85546875" style="1" customWidth="1"/>
-    <x:col min="15" max="15" width="18.4296875" style="1" customWidth="1"/>
-    <x:col min="16" max="16" width="17.14453125" style="1" customWidth="1"/>
-    <x:col min="17" max="16384" width="12.54296875" style="1"/>
+    <x:col min="15" max="16" width="22.28515625" style="1" customWidth="1"/>
+    <x:col min="17" max="17" width="18.4296875" style="1" customWidth="1"/>
+    <x:col min="18" max="18" width="17.14453125" style="1" customWidth="1"/>
+    <x:col min="19" max="16384" width="12.54296875" style="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:14" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="N1" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="O1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:16" ht="13.199999999999999">
+      <x:c r="P1" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:18" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
         <x:v>25</x:v>
@@ -1021,74 +1037,86 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="P2" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:16" s="7" customFormat="1" ht="15.75" customHeight="1">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="Q2" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="R2" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:18" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D3" s="2" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E3" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F3" s="7" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G3" s="7" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H3" s="7" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="I3" s="7" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="J3" s="7" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B3" s="2" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C3" s="2" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D3" s="2" t="s">
+      <x:c r="K3" s="7" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L3" s="7" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="M3" s="7" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="N3" s="7" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="O3" s="7" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="P3" s="7" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="Q3" s="7" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="E3" s="2" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="F3" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G3" s="7" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H3" s="7" t="s">
+      <x:c r="R3" s="7" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:18" ht="15.75" customHeight="1">
+      <x:c r="A4" s="3" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B4" s="3" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C4" s="3" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D4" s="5" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="I3" s="7" t="s">
+      <x:c r="E4" s="5" t="s">
         <x:v>44</x:v>
-      </x:c>
-      <x:c r="J3" s="7" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="K3" s="7" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L3" s="7" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="M3" s="7" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="N3" s="7" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="O3" s="7" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="P3" s="7" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:16" ht="15.75" customHeight="1">
-      <x:c r="A4" s="3" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="B4" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="3" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D4" s="5" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E4" s="5" t="s">
-        <x:v>51</x:v>
       </x:c>
       <x:c r="F4" s="1">
         <x:v>150</x:v>
@@ -1118,27 +1146,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="O4" s="1">
+        <x:v>0.32000000000000001</x:v>
+      </x:c>
+      <x:c r="P4" s="1">
+        <x:v>0.47999999999999998</x:v>
+      </x:c>
+      <x:c r="Q4" s="1">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="P4" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="R4" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D5" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E5" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F5" s="1">
         <x:v>150</x:v>
@@ -1168,27 +1202,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="O5" s="1">
+        <x:v>0.32000000000000001</x:v>
+      </x:c>
+      <x:c r="P5" s="1">
+        <x:v>0.47999999999999998</x:v>
+      </x:c>
+      <x:c r="Q5" s="1">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P5" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="R5" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B6" s="5" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C6" s="5" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D6" s="5" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B6" s="5" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C6" s="5" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D6" s="5" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="E6" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F6" s="1">
         <x:v>170</x:v>
@@ -1218,27 +1258,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="O6" s="1">
+        <x:v>0.32000000000000001</x:v>
+      </x:c>
+      <x:c r="P6" s="1">
+        <x:v>0.47999999999999998</x:v>
+      </x:c>
+      <x:c r="Q6" s="1">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P6" s="1" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="R6" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>31</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C7" s="5" t="s">
-        <x:v>26</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D7" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E7" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F7" s="1">
         <x:v>250</x:v>
@@ -1268,27 +1314,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="O7" s="1">
+        <x:v>0.32000000000000001</x:v>
+      </x:c>
+      <x:c r="P7" s="1">
+        <x:v>0.47999999999999998</x:v>
+      </x:c>
+      <x:c r="Q7" s="1">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P7" s="1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="R7" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>6</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C8" s="5" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D8" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E8" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F8" s="1">
         <x:v>270</x:v>
@@ -1318,27 +1370,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="O8" s="1">
+        <x:v>0.32000000000000001</x:v>
+      </x:c>
+      <x:c r="P8" s="1">
+        <x:v>0.47999999999999998</x:v>
+      </x:c>
+      <x:c r="Q8" s="1">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P8" s="1" t="s">
+      <x:c r="R8" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:18" ht="15.75" customHeight="1">
+      <x:c r="A9" s="5" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B9" s="5" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C9" s="5" t="s">
         <x:v>50</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" spans="1:16" ht="15.75" customHeight="1">
-      <x:c r="A9" s="5" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="B9" s="5" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C9" s="5" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="D9" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E9" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F9" s="1">
         <x:v>300</x:v>
@@ -1368,27 +1426,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="O9" s="1">
+        <x:v>0.32000000000000001</x:v>
+      </x:c>
+      <x:c r="P9" s="1">
+        <x:v>0.47999999999999998</x:v>
+      </x:c>
+      <x:c r="Q9" s="1">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P9" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="R9" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C10" s="5" t="s">
-        <x:v>40</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D10" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E10" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F10" s="1">
         <x:v>350</x:v>
@@ -1418,27 +1482,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="O10" s="1">
+        <x:v>0.32000000000000001</x:v>
+      </x:c>
+      <x:c r="P10" s="1">
+        <x:v>0.47999999999999998</x:v>
+      </x:c>
+      <x:c r="Q10" s="1">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P10" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:16" ht="15.75" customHeight="1">
+      <x:c r="R10" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A11" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F11" s="1">
         <x:v>400</x:v>
@@ -1468,10 +1538,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="O11" s="1">
+        <x:v>0.32000000000000001</x:v>
+      </x:c>
+      <x:c r="P11" s="1">
+        <x:v>0.47999999999999998</x:v>
+      </x:c>
+      <x:c r="Q11" s="1">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P11" s="1" t="s">
-        <x:v>2</x:v>
+      <x:c r="R11" s="1" t="s">
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/FighterData.xlsx
+++ b/JsonConverter/ExcelFiles/FighterData.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="13035"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="12795"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="FighterData" sheetId="1" r:id="rId4"/>
@@ -19,174 +19,177 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="56">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="57">
+  <x:si>
+    <x:t>fighter_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BodyAddress</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김기본</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김종합</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김타격</x:t>
+  </x:si>
+  <x:si>
+    <x:t>리치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Step</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_elbow,skill_uppercut,skill_takedown_judo,skill_guillotine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_elbow,skill_uppercut,skill_takedown_judo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WrestlingDefense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_takedown_judo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WrestlingOffense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StartingSkillIds</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_guillotine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 캐릭터이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>션 스트릭랜드</x:t>
+  </x:si>
   <x:si>
     <x:t>선호사거리</x:t>
   </x:si>
   <x:si>
-    <x:t>skill_takedown_judo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StartingSkillIds</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WrestlingDefense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_guillotine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WrestlingOffense</x:t>
+    <x:t>김그래플러</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Stamina</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김주짓수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Reach</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타격위주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김클린치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김레슬러</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레슬링위주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클린치위주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주짓수위주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JiuJitsuDefense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구현된 특수기술 전체 테스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TrainingStamina</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StandingDefense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레슬링과 Ground 테스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타격, 테이크다운 방어 위주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PortraitAddress</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StandingOffense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JiuJitsuOffense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KimBasic[south-east 1_0]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_elbow,skill_uppercut</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KimBasic[south-east 1_1]</x:t>
   </x:si>
   <x:si>
     <x:t>PreferredMinDistance</x:t>
   </x:si>
   <x:si>
     <x:t>PreferredMaxDistance</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>리치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김종합</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김기본</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김타격</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_elbow,skill_uppercut,skill_takedown_judo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_elbow,skill_uppercut,skill_takedown_judo,skill_guillotine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BodyAddress</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 캐릭터이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>션 스트릭랜드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>클린치위주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김그래플러</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김클린치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Reach</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김주짓수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레슬링위주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타격위주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주짓수위주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김레슬러</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Stamina</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KimBasic[south-east 1_0]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KimBasic[south-east 1_1]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_elbow,skill_uppercut</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타격, 테이크다운 방어 위주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TrainingStamina</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JiuJitsuOffense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레슬링과 Ground 테스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StandingOffense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StandingDefense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PortraitAddress</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구현된 특수기술 전체 테스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JiuJitsuDefense</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -957,7 +960,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:R35"/>
+  <x:dimension ref="A1:S35"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="25.4296875" style="1" customWidth="1"/>
@@ -970,153 +973,159 @@
     <x:col min="10" max="10" width="18.85546875" style="1" customWidth="1"/>
     <x:col min="11" max="12" width="18" style="1" customWidth="1"/>
     <x:col min="13" max="14" width="18.85546875" style="1" customWidth="1"/>
-    <x:col min="15" max="16" width="22.28515625" style="1" customWidth="1"/>
-    <x:col min="17" max="17" width="18.4296875" style="1" customWidth="1"/>
-    <x:col min="18" max="18" width="17.14453125" style="1" customWidth="1"/>
-    <x:col min="19" max="16384" width="12.54296875" style="1"/>
+    <x:col min="15" max="17" width="22.28515625" style="1" customWidth="1"/>
+    <x:col min="18" max="18" width="18.4296875" style="1" customWidth="1"/>
+    <x:col min="19" max="19" width="17.14453125" style="1" customWidth="1"/>
+    <x:col min="20" max="16384" width="12.54296875" style="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="N1" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="O1" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="P1" s="1" t="s">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:18" ht="13.199999999999999">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:19" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="J2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="L2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="M2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="N2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="O2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="P2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="Q2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="R2" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:18" s="7" customFormat="1" ht="15.75" customHeight="1">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="S2" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:19" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
         <x:v>33</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D3" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E3" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F3" s="7" t="s">
-        <x:v>10</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G3" s="7" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H3" s="7" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I3" s="7" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="J3" s="7" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="K3" s="7" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L3" s="7" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="I3" s="7" t="s">
+      <x:c r="M3" s="7" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="N3" s="7" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="O3" s="7" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="P3" s="7" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="Q3" s="7" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="R3" s="7" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="S3" s="7" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:19" ht="15.75" customHeight="1">
+      <x:c r="A4" s="3" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B4" s="3" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C4" s="3" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D4" s="5" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E4" s="5" t="s">
         <x:v>52</x:v>
-      </x:c>
-      <x:c r="J3" s="7" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="K3" s="7" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="L3" s="7" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="M3" s="7" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="N3" s="7" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="O3" s="7" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="P3" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="Q3" s="7" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="R3" s="7" t="s">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A4" s="3" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B4" s="3" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C4" s="3" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D4" s="5" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="E4" s="5" t="s">
-        <x:v>44</x:v>
       </x:c>
       <x:c r="F4" s="1">
         <x:v>150</x:v>
@@ -1152,27 +1161,30 @@
         <x:v>0.47999999999999998</x:v>
       </x:c>
       <x:c r="Q4" s="1">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="R4" s="1">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="R4" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:18" ht="15.75" customHeight="1">
+      <x:c r="S4" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>27</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D5" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E5" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F5" s="1">
         <x:v>150</x:v>
@@ -1208,27 +1220,30 @@
         <x:v>0.47999999999999998</x:v>
       </x:c>
       <x:c r="Q5" s="1">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="R5" s="1">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R5" s="1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:18" ht="15.75" customHeight="1">
+      <x:c r="S5" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>31</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D6" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E6" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F6" s="1">
         <x:v>170</x:v>
@@ -1264,27 +1279,30 @@
         <x:v>0.47999999999999998</x:v>
       </x:c>
       <x:c r="Q6" s="1">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="R6" s="1">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R6" s="1" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:18" ht="15.75" customHeight="1">
+      <x:c r="S6" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C7" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D7" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E7" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F7" s="1">
         <x:v>250</x:v>
@@ -1320,27 +1338,30 @@
         <x:v>0.47999999999999998</x:v>
       </x:c>
       <x:c r="Q7" s="1">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="R7" s="1">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R7" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:18" ht="15.75" customHeight="1">
+      <x:c r="S7" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>39</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C8" s="5" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D8" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E8" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F8" s="1">
         <x:v>270</x:v>
@@ -1376,27 +1397,30 @@
         <x:v>0.47999999999999998</x:v>
       </x:c>
       <x:c r="Q8" s="1">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="R8" s="1">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R8" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:18" ht="15.75" customHeight="1">
+      <x:c r="S8" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A9" s="5" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C9" s="5" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D9" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E9" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F9" s="1">
         <x:v>300</x:v>
@@ -1432,27 +1456,30 @@
         <x:v>0.47999999999999998</x:v>
       </x:c>
       <x:c r="Q9" s="1">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="R9" s="1">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R9" s="1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:18" ht="15.75" customHeight="1">
+      <x:c r="S9" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C10" s="5" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D10" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E10" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F10" s="1">
         <x:v>350</x:v>
@@ -1488,27 +1515,30 @@
         <x:v>0.47999999999999998</x:v>
       </x:c>
       <x:c r="Q10" s="1">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="R10" s="1">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R10" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:18" ht="15.75" customHeight="1">
+      <x:c r="S10" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A11" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F11" s="1">
         <x:v>400</x:v>
@@ -1544,10 +1574,13 @@
         <x:v>0.47999999999999998</x:v>
       </x:c>
       <x:c r="Q11" s="1">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="R11" s="1">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R11" s="1" t="s">
-        <x:v>15</x:v>
+      <x:c r="S11" s="1" t="s">
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5" ht="15.75" customHeight="1">
